--- a/notebooks/data/kalshi_cpi_results.xlsx
+++ b/notebooks/data/kalshi_cpi_results.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\OneDrive\Documenten\UA\Data engineering\KALSHI_PROJECT\Kalshi_economics\notebooks\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3344541B-3118-467B-A12A-81C28AF197F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2355" yWindow="2355" windowWidth="17280" windowHeight="8925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -247,8 +253,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,13 +317,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -355,7 +369,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -389,6 +403,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -423,9 +438,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -598,11 +614,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -630,19 +649,19 @@
         <v>41</v>
       </c>
       <c r="C2">
-        <v>2.698039215686274</v>
+        <v>2.6980392156862738</v>
       </c>
       <c r="D2">
-        <v>2.391201432150014</v>
+        <v>2.3912014321500141</v>
       </c>
       <c r="E2">
-        <v>0.3068</v>
+        <v>0.30680000000000002</v>
       </c>
       <c r="F2">
-        <v>0.3068</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.30680000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -650,19 +669,19 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>2.928846153846154</v>
+        <v>2.9288461538461541</v>
       </c>
       <c r="D3">
-        <v>2.653304114557753</v>
+        <v>2.6533041145577529</v>
       </c>
       <c r="E3">
-        <v>0.2755</v>
+        <v>0.27550000000000002</v>
       </c>
       <c r="F3">
-        <v>0.2755</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.27550000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -670,19 +689,19 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>3.043137254901961</v>
+        <v>3.0431372549019611</v>
       </c>
       <c r="D4">
-        <v>2.696443916493951</v>
+        <v>2.6964439164939509</v>
       </c>
       <c r="E4">
-        <v>0.3467</v>
+        <v>0.34670000000000001</v>
       </c>
       <c r="F4">
-        <v>0.3467</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.34670000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -690,19 +709,19 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2.995098039215686</v>
+        <v>2.9950980392156858</v>
       </c>
       <c r="D5">
-        <v>2.729136238202212</v>
+        <v>2.7291362382022122</v>
       </c>
       <c r="E5">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="F5">
-        <v>0.266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.26600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -722,7 +741,7 @@
         <v>0.2036</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -736,13 +755,13 @@
         <v>2.938591743031616</v>
       </c>
       <c r="E7">
-        <v>-0.1926</v>
+        <v>-0.19259999999999999</v>
       </c>
       <c r="F7">
-        <v>0.1926</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.19259999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -750,10 +769,10 @@
         <v>47</v>
       </c>
       <c r="C8">
-        <v>2.585643564356435</v>
+        <v>2.5856435643564351</v>
       </c>
       <c r="D8">
-        <v>2.742618052167134</v>
+        <v>2.7426180521671339</v>
       </c>
       <c r="E8">
         <v>-0.157</v>
@@ -762,7 +781,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -773,16 +792,16 @@
         <v>2.38495145631068</v>
       </c>
       <c r="D9">
-        <v>2.680453865910226</v>
+        <v>2.6804538659102262</v>
       </c>
       <c r="E9">
-        <v>-0.2955</v>
+        <v>-0.29549999999999998</v>
       </c>
       <c r="F9">
-        <v>0.2955</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.29549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -790,19 +809,19 @@
         <v>49</v>
       </c>
       <c r="C10">
-        <v>2.341</v>
+        <v>2.3410000000000002</v>
       </c>
       <c r="D10">
-        <v>2.377265107368087</v>
+        <v>2.3772651073680868</v>
       </c>
       <c r="E10">
-        <v>-0.0363</v>
+        <v>-3.6299999999999999E-2</v>
       </c>
       <c r="F10">
-        <v>0.0363</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>3.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -810,19 +829,19 @@
         <v>50</v>
       </c>
       <c r="C11">
-        <v>2.48425925925926</v>
+        <v>2.4842592592592601</v>
       </c>
       <c r="D11">
-        <v>2.32538823025783</v>
+        <v>2.3253882302578299</v>
       </c>
       <c r="E11">
-        <v>0.1589</v>
+        <v>0.15890000000000001</v>
       </c>
       <c r="F11">
-        <v>0.1589</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.15890000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -833,16 +852,16 @@
         <v>2.83076923076923</v>
       </c>
       <c r="D12">
-        <v>2.381981462805549</v>
+        <v>2.3819814628055491</v>
       </c>
       <c r="E12">
-        <v>0.4488</v>
+        <v>0.44879999999999998</v>
       </c>
       <c r="F12">
-        <v>0.4488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.44879999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -850,19 +869,19 @@
         <v>52</v>
       </c>
       <c r="C13">
-        <v>2.312564102564102</v>
+        <v>2.3125641025641022</v>
       </c>
       <c r="D13">
-        <v>2.801583447761335</v>
+        <v>2.8015834477613351</v>
       </c>
       <c r="E13">
-        <v>-0.489</v>
+        <v>-0.48899999999999999</v>
       </c>
       <c r="F13">
-        <v>0.489</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.48899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -873,16 +892,16 @@
         <v>2.502261306532664</v>
       </c>
       <c r="D14">
-        <v>2.990978307899961</v>
+        <v>2.9909783078999612</v>
       </c>
       <c r="E14">
-        <v>-0.4887</v>
+        <v>-0.48870000000000002</v>
       </c>
       <c r="F14">
-        <v>0.4887</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>0.48870000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -890,10 +909,10 @@
         <v>54</v>
       </c>
       <c r="C15">
-        <v>2.684000000000001</v>
+        <v>2.6840000000000011</v>
       </c>
       <c r="D15">
-        <v>2.870690967509981</v>
+        <v>2.8706909675099812</v>
       </c>
       <c r="E15">
         <v>-0.1867</v>
@@ -902,7 +921,7 @@
         <v>0.1867</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -910,19 +929,19 @@
         <v>55</v>
       </c>
       <c r="C16">
-        <v>2.656201550387597</v>
+        <v>2.6562015503875971</v>
       </c>
       <c r="D16">
-        <v>2.719472461284833</v>
+        <v>2.7194724612848331</v>
       </c>
       <c r="E16">
-        <v>-0.0633</v>
+        <v>-6.3299999999999995E-2</v>
       </c>
       <c r="F16">
-        <v>0.0633</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>6.3299999999999995E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -933,16 +952,16 @@
         <v>2.321153846153845</v>
       </c>
       <c r="D17">
-        <v>2.578844053871343</v>
+        <v>2.5788440538713431</v>
       </c>
       <c r="E17">
-        <v>-0.2577</v>
+        <v>-0.25769999999999998</v>
       </c>
       <c r="F17">
-        <v>0.2577</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.25769999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -950,19 +969,19 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>2.548360655737705</v>
+        <v>2.5483606557377052</v>
       </c>
       <c r="D18">
-        <v>2.426483031541671</v>
+        <v>2.4264830315416712</v>
       </c>
       <c r="E18">
-        <v>0.1219</v>
+        <v>0.12189999999999999</v>
       </c>
       <c r="F18">
-        <v>0.1219</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.12189999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -973,16 +992,16 @@
         <v>2.891</v>
       </c>
       <c r="D19">
-        <v>2.607144490692037</v>
+        <v>2.6071444906920371</v>
       </c>
       <c r="E19">
-        <v>0.2839</v>
+        <v>0.28389999999999999</v>
       </c>
       <c r="F19">
-        <v>0.2839</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.28389999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -993,7 +1012,7 @@
         <v>3.06078431372549</v>
       </c>
       <c r="D20">
-        <v>2.941475793558301</v>
+        <v>2.9414757935583009</v>
       </c>
       <c r="E20">
         <v>0.1193</v>
@@ -1002,7 +1021,7 @@
         <v>0.1193</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1010,7 +1029,7 @@
         <v>60</v>
       </c>
       <c r="C21">
-        <v>3.166019417475728</v>
+        <v>3.1660194174757281</v>
       </c>
       <c r="D21">
         <v>2.970257948647093</v>
@@ -1022,7 +1041,7 @@
         <v>0.1958</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1042,7 +1061,7 @@
         <v>0.1636</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1053,7 +1072,7 @@
         <v>3.032673267326734</v>
       </c>
       <c r="D23">
-        <v>3.360795126219673</v>
+        <v>3.3607951262196729</v>
       </c>
       <c r="E23">
         <v>-0.3281</v>
@@ -1062,7 +1081,7 @@
         <v>0.3281</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1073,16 +1092,16 @@
         <v>2.798</v>
       </c>
       <c r="D24">
-        <v>3.486834912083658</v>
+        <v>3.4868349120836579</v>
       </c>
       <c r="E24">
-        <v>-0.6888</v>
+        <v>-0.68879999999999997</v>
       </c>
       <c r="F24">
-        <v>0.6888</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>0.68879999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1090,10 +1109,10 @@
         <v>64</v>
       </c>
       <c r="C25">
-        <v>2.929</v>
+        <v>2.9289999999999998</v>
       </c>
       <c r="D25">
-        <v>3.157074141648697</v>
+        <v>3.1570741416486969</v>
       </c>
       <c r="E25">
         <v>-0.2281</v>
@@ -1102,7 +1121,7 @@
         <v>0.2281</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1110,19 +1129,19 @@
         <v>65</v>
       </c>
       <c r="C26">
-        <v>3.004634146341463</v>
+        <v>3.0046341463414632</v>
       </c>
       <c r="D26">
         <v>3.08834298648557</v>
       </c>
       <c r="E26">
-        <v>-0.0837</v>
+        <v>-8.3699999999999997E-2</v>
       </c>
       <c r="F26">
-        <v>0.0837</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>8.3699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1130,10 +1149,10 @@
         <v>66</v>
       </c>
       <c r="C27">
-        <v>2.950334448160535</v>
+        <v>2.9503344481605351</v>
       </c>
       <c r="D27">
-        <v>3.133346274591187</v>
+        <v>3.1333462745911871</v>
       </c>
       <c r="E27">
         <v>-0.183</v>
@@ -1142,7 +1161,7 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1150,19 +1169,19 @@
         <v>67</v>
       </c>
       <c r="C28">
-        <v>3.551818181818182</v>
+        <v>3.5518181818181822</v>
       </c>
       <c r="D28">
-        <v>3.687206638119256</v>
+        <v>3.6872066381192559</v>
       </c>
       <c r="E28">
-        <v>-0.1354</v>
+        <v>-0.13539999999999999</v>
       </c>
       <c r="F28">
-        <v>0.1354</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>0.13539999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1173,16 +1192,16 @@
         <v>2.427021276595744</v>
       </c>
       <c r="D29">
-        <v>3.722504803505289</v>
+        <v>3.7225048035052888</v>
       </c>
       <c r="E29">
-        <v>-1.2955</v>
+        <v>-1.2955000000000001</v>
       </c>
       <c r="F29">
-        <v>1.2955</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>1.2955000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1190,19 +1209,19 @@
         <v>69</v>
       </c>
       <c r="C30">
-        <v>2.998076923076923</v>
+        <v>2.9980769230769231</v>
       </c>
       <c r="D30">
-        <v>3.287749268428297</v>
+        <v>3.2877492684282972</v>
       </c>
       <c r="E30">
-        <v>-0.2897</v>
+        <v>-0.28970000000000001</v>
       </c>
       <c r="F30">
-        <v>0.2897</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>0.28970000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1210,19 +1229,19 @@
         <v>70</v>
       </c>
       <c r="C31">
-        <v>3.636868611111112</v>
+        <v>3.6368686111111121</v>
       </c>
       <c r="D31">
         <v>3.070617072997095</v>
       </c>
       <c r="E31">
-        <v>0.5663</v>
+        <v>0.56630000000000003</v>
       </c>
       <c r="F31">
-        <v>0.5663</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>0.56630000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1236,13 +1255,13 @@
         <v>4.131851231385042</v>
       </c>
       <c r="E32">
-        <v>-1.6767</v>
+        <v>-1.6767000000000001</v>
       </c>
       <c r="F32">
-        <v>1.6767</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>1.6767000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1250,10 +1269,10 @@
         <v>72</v>
       </c>
       <c r="C33">
-        <v>4.327073170731706</v>
+        <v>4.3270731707317056</v>
       </c>
       <c r="D33">
-        <v>4.950079879124369</v>
+        <v>4.9500798791243694</v>
       </c>
       <c r="E33">
         <v>-0.623</v>
@@ -1262,7 +1281,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -1270,19 +1289,19 @@
         <v>73</v>
       </c>
       <c r="C34">
-        <v>5.251530612244897</v>
+        <v>5.2515306122448973</v>
       </c>
       <c r="D34">
-        <v>4.917719362889961</v>
+        <v>4.9177193628899607</v>
       </c>
       <c r="E34">
-        <v>0.3338</v>
+        <v>0.33379999999999999</v>
       </c>
       <c r="F34">
-        <v>0.3338</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>0.33379999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1290,19 +1309,19 @@
         <v>74</v>
       </c>
       <c r="C35">
-        <v>5.819597069597069</v>
+        <v>5.8195970695970693</v>
       </c>
       <c r="D35">
-        <v>5.957820738137087</v>
+        <v>5.9578207381370873</v>
       </c>
       <c r="E35">
-        <v>-0.1382</v>
+        <v>-0.13819999999999999</v>
       </c>
       <c r="F35">
-        <v>0.1382</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>0.13819999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1316,10 +1335,10 @@
         <v>6.327178517960097</v>
       </c>
       <c r="E36">
-        <v>0.0337</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="F36">
-        <v>0.0337</v>
+        <v>3.3700000000000001E-2</v>
       </c>
     </row>
   </sheetData>
